--- a/inputs/data_symbols_TD/07_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5_delta_t_60s.xlsx
+++ b/inputs/data_symbols_TD/07_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5_delta_t_60s.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AEF5269-7A3F-49D6-9D2B-5667C2BF5FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5CE224F-4811-4F6A-87A8-7162DA074389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{87657F9C-7A15-4B73-A661-EE13BDF257C9}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{5CC10C9C-F663-40F5-A374-5CEAB07BFD2D}"/>
   </bookViews>
   <sheets>
     <sheet name="07_LTAN06_800km_1213COLD_MZ_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F28EC09-7AD3-4DBE-9D65-E7FD2A73017C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D032B1-AC77-4231-9B18-9CDCD55928E6}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>25.068339999999999</v>
+        <v>24.92578</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>25.068339999999999</v>
+        <v>24.92578</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>25.07404</v>
+        <v>24.931429999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>25.089860000000002</v>
+        <v>24.94717</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>25.113600000000002</v>
+        <v>24.970780000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>25.14367</v>
+        <v>25.000689999999999</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>25.17886</v>
+        <v>25.035699999999999</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>25.218240000000002</v>
+        <v>25.07488</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>25.261030000000002</v>
+        <v>25.11749</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>25.306640000000002</v>
+        <v>25.162949999999999</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>25.354579999999999</v>
+        <v>25.210799999999999</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>25.404489999999999</v>
+        <v>25.260629999999999</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>25.456019999999999</v>
+        <v>25.312080000000002</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>25.508900000000001</v>
+        <v>25.364850000000001</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>25.562889999999999</v>
+        <v>25.418690000000002</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>25.617799999999999</v>
+        <v>25.473389999999998</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>25.67343</v>
+        <v>25.5288</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>25.729600000000001</v>
+        <v>25.58475</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>25.786149999999999</v>
+        <v>25.64113</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>25.806560000000001</v>
+        <v>25.661570000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>25.76286</v>
+        <v>25.618310000000001</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>25.669619999999998</v>
+        <v>25.52581</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="D24">
-        <v>25.53753</v>
+        <v>25.394639999999999</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>25.37471</v>
+        <v>25.232780000000002</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>25.18749</v>
+        <v>25.046500000000002</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>24.98086</v>
+        <v>24.840779999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>24.758790000000001</v>
+        <v>24.61964</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>24.524470000000001</v>
+        <v>24.38627</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>24.280480000000001</v>
+        <v>24.143270000000001</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>24.028960000000001</v>
+        <v>23.89274</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>23.77169</v>
+        <v>23.636430000000001</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>23.51013</v>
+        <v>23.375779999999999</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -1479,7 +1479,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>23.245509999999999</v>
+        <v>23.111979999999999</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>22.9788</v>
+        <v>22.846019999999999</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>22.710789999999999</v>
+        <v>22.578720000000001</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
@@ -1521,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>22.442170000000001</v>
+        <v>22.310770000000002</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>22.20947</v>
+        <v>22.078510000000001</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>22.040759999999999</v>
+        <v>21.909859999999998</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>21.922000000000001</v>
+        <v>21.790890000000001</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>21.842949999999998</v>
+        <v>21.711480000000002</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>21.795850000000002</v>
+        <v>21.66395</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>21.774650000000001</v>
+        <v>21.64228</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>21.774529999999999</v>
+        <v>21.641670000000001</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>21.79158</v>
+        <v>21.65822</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>21.822649999999999</v>
+        <v>21.688790000000001</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>21.865159999999999</v>
+        <v>21.730789999999999</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>21.916989999999998</v>
+        <v>21.782080000000001</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>21.976379999999999</v>
+        <v>21.84093</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>22.041879999999999</v>
+        <v>21.90588</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>22.112259999999999</v>
+        <v>21.9757</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>22.18646</v>
+        <v>22.049330000000001</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>22.263580000000001</v>
+        <v>22.125900000000001</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>22.34291</v>
+        <v>22.204689999999999</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>22.423870000000001</v>
+        <v>22.285150000000002</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>22.505980000000001</v>
+        <v>22.366779999999999</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>22.588819999999998</v>
+        <v>22.449169999999999</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>22.672029999999999</v>
+        <v>22.531980000000001</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>22.755299999999998</v>
+        <v>22.614889999999999</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>22.838339999999999</v>
+        <v>22.697610000000001</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>22.92089</v>
+        <v>22.779890000000002</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>23.002749999999999</v>
+        <v>22.861519999999999</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>23.083780000000001</v>
+        <v>22.942319999999999</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>23.163830000000001</v>
+        <v>23.02214</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>23.242809999999999</v>
+        <v>23.100860000000001</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>23.320589999999999</v>
+        <v>23.1784</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>23.397079999999999</v>
+        <v>23.254660000000001</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>23.47221</v>
+        <v>23.32959</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>23.545940000000002</v>
+        <v>23.40314</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>23.61825</v>
+        <v>23.475280000000001</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>23.689139999999998</v>
+        <v>23.546009999999999</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>23.758600000000001</v>
+        <v>23.615320000000001</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>23.826650000000001</v>
+        <v>23.683219999999999</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>23.89331</v>
+        <v>23.749739999999999</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>23.95862</v>
+        <v>23.814900000000002</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>24.02261</v>
+        <v>23.878720000000001</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>24.085319999999999</v>
+        <v>23.94126</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>24.146799999999999</v>
+        <v>24.002569999999999</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>24.20712</v>
+        <v>24.0627</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>24.266349999999999</v>
+        <v>24.121749999999999</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>24.324539999999999</v>
+        <v>24.179790000000001</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>24.381779999999999</v>
+        <v>24.236889999999999</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>24.43815</v>
+        <v>24.293119999999998</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>24.49371</v>
+        <v>24.34853</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>24.548549999999999</v>
+        <v>24.403220000000001</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>24.60275</v>
+        <v>24.457260000000002</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>24.656389999999998</v>
+        <v>24.510739999999998</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>24.709569999999999</v>
+        <v>24.563759999999998</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>24.762350000000001</v>
+        <v>24.616409999999998</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>24.814810000000001</v>
+        <v>24.668759999999999</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>24.86703</v>
+        <v>24.720890000000001</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>24.919080000000001</v>
+        <v>24.772860000000001</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>24.97101</v>
+        <v>24.824719999999999</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>25.022849999999998</v>
+        <v>24.876529999999999</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>25.074660000000002</v>
+        <v>24.92831</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>25.126460000000002</v>
+        <v>24.9801</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>25.178290000000001</v>
+        <v>25.031929999999999</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>25.230160000000001</v>
+        <v>25.08381</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>25.2821</v>
+        <v>25.135739999999998</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>25.334060000000001</v>
+        <v>25.187709999999999</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>25.386040000000001</v>
+        <v>25.239699999999999</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>25.437999999999999</v>
+        <v>25.29166</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>25.489909999999998</v>
+        <v>25.343579999999999</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>25.54176</v>
+        <v>25.395389999999999</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>25.59348</v>
+        <v>25.447089999999999</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>25.645060000000001</v>
+        <v>25.498640000000002</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>25.696480000000001</v>
+        <v>25.55003</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>25.74776</v>
+        <v>25.60125</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>25.79888</v>
+        <v>25.65231</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>25.84984</v>
+        <v>25.703230000000001</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>25.900639999999999</v>
+        <v>25.75403</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>25.9513</v>
+        <v>25.80472</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>26.001840000000001</v>
+        <v>25.855319999999999</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>26.05227</v>
+        <v>25.90579</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>26.102599999999999</v>
+        <v>25.956140000000001</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>26.152830000000002</v>
+        <v>26.006319999999999</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>26.202960000000001</v>
+        <v>26.056349999999998</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>26.252960000000002</v>
+        <v>26.10623</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>26.302790000000002</v>
+        <v>26.155950000000001</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>26.352429999999998</v>
+        <v>26.205500000000001</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
@@ -2697,7 +2697,7 @@
         <v>3</v>
       </c>
       <c r="D121">
-        <v>26.365400000000001</v>
+        <v>26.218599999999999</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -2711,7 +2711,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>26.313790000000001</v>
+        <v>26.16751</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="D123">
-        <v>26.212340000000001</v>
+        <v>26.066890000000001</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>26.07179</v>
+        <v>25.927320000000002</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
@@ -2753,7 +2753,7 @@
         <v>3</v>
       </c>
       <c r="D125">
-        <v>25.900320000000001</v>
+        <v>25.756889999999999</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D126">
-        <v>25.704339999999998</v>
+        <v>25.561920000000001</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
@@ -2781,7 +2781,7 @@
         <v>3</v>
       </c>
       <c r="D127">
-        <v>25.488880000000002</v>
+        <v>25.347439999999999</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
@@ -2795,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="D128">
-        <v>25.257960000000001</v>
+        <v>25.1175</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>25.014800000000001</v>
+        <v>24.875350000000001</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
@@ -2823,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="D130">
-        <v>24.76201</v>
+        <v>24.6236</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="D131">
-        <v>24.501740000000002</v>
+        <v>24.364370000000001</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
@@ -2851,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="D132">
-        <v>24.235800000000001</v>
+        <v>24.099450000000001</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>23.965679999999999</v>
+        <v>23.830269999999999</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>23.692599999999999</v>
+        <v>23.558050000000001</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
@@ -2893,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="D135">
-        <v>23.417539999999999</v>
+        <v>23.28379</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="D136">
-        <v>23.14132</v>
+        <v>23.008320000000001</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="D137">
-        <v>22.864619999999999</v>
+        <v>22.732330000000001</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>22.623989999999999</v>
+        <v>22.492180000000001</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>22.44754</v>
+        <v>22.315809999999999</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>22.321179999999998</v>
+        <v>22.18928</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>22.234690000000001</v>
+        <v>22.102460000000001</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>22.180289999999999</v>
+        <v>22.04766</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>22.15193</v>
+        <v>22.01886</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>22.144770000000001</v>
+        <v>22.011240000000001</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>22.154920000000001</v>
+        <v>22.020910000000001</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>22.179220000000001</v>
+        <v>22.044730000000001</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>22.21508</v>
+        <v>22.080100000000002</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>22.260380000000001</v>
+        <v>22.124890000000001</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>22.313369999999999</v>
+        <v>22.17736</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>22.372589999999999</v>
+        <v>22.236049999999999</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>22.436800000000002</v>
+        <v>22.299720000000001</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>22.504950000000001</v>
+        <v>22.367319999999999</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>22.576139999999999</v>
+        <v>22.43798</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>22.649660000000001</v>
+        <v>22.51098</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>22.724930000000001</v>
+        <v>22.585760000000001</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>22.801459999999999</v>
+        <v>22.661819999999999</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>22.878830000000001</v>
+        <v>22.738759999999999</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>22.956679999999999</v>
+        <v>22.816230000000001</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>23.034700000000001</v>
+        <v>22.893899999999999</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>23.11261</v>
+        <v>22.971499999999999</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>23.19013</v>
+        <v>23.048770000000001</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>23.26707</v>
+        <v>23.125489999999999</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>23.34328</v>
+        <v>23.20149</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>23.41863</v>
+        <v>23.276610000000002</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>23.492989999999999</v>
+        <v>23.350729999999999</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>23.566269999999999</v>
+        <v>23.423770000000001</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>23.638349999999999</v>
+        <v>23.495640000000002</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>23.70917</v>
+        <v>23.56626</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>23.778690000000001</v>
+        <v>23.63561</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>23.846879999999999</v>
+        <v>23.70364</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>23.913740000000001</v>
+        <v>23.770350000000001</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>23.97926</v>
+        <v>23.835740000000001</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>24.043469999999999</v>
+        <v>23.899809999999999</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>24.106369999999998</v>
+        <v>23.962569999999999</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>24.168009999999999</v>
+        <v>24.024059999999999</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>24.22841</v>
+        <v>24.084309999999999</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>24.287610000000001</v>
+        <v>24.143350000000002</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>24.345669999999998</v>
+        <v>24.201229999999999</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>24.402640000000002</v>
+        <v>24.258019999999998</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>24.458590000000001</v>
+        <v>24.31381</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>24.5136</v>
+        <v>24.368659999999998</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>24.567720000000001</v>
+        <v>24.422640000000001</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>24.621030000000001</v>
+        <v>24.475829999999998</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>24.67362</v>
+        <v>24.528279999999999</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>24.725549999999998</v>
+        <v>24.58006</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>24.776910000000001</v>
+        <v>24.631260000000001</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>24.827780000000001</v>
+        <v>24.68197</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>24.878240000000002</v>
+        <v>24.732279999999999</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>24.928370000000001</v>
+        <v>24.78229</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>24.978249999999999</v>
+        <v>24.832059999999998</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>25.027940000000001</v>
+        <v>24.88167</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>25.07752</v>
+        <v>24.931170000000002</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>25.127030000000001</v>
+        <v>24.980619999999998</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>25.17652</v>
+        <v>25.030069999999998</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>25.226019999999998</v>
+        <v>25.079550000000001</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>25.275569999999998</v>
+        <v>25.129090000000001</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>25.325189999999999</v>
+        <v>25.178719999999998</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>25.374919999999999</v>
+        <v>25.228459999999998</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>25.42475</v>
+        <v>25.278289999999998</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>25.47467</v>
+        <v>25.328209999999999</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>25.524629999999998</v>
+        <v>25.37819</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>25.574629999999999</v>
+        <v>25.4282</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>25.62462</v>
+        <v>25.478190000000001</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>25.674589999999998</v>
+        <v>25.52814</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>25.724489999999999</v>
+        <v>25.577999999999999</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>25.774270000000001</v>
+        <v>25.627759999999999</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>25.823930000000001</v>
+        <v>25.677399999999999</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>25.8735</v>
+        <v>25.72691</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>25.922940000000001</v>
+        <v>25.776299999999999</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>25.972259999999999</v>
+        <v>25.825569999999999</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>26.021460000000001</v>
+        <v>25.874770000000002</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>26.070550000000001</v>
+        <v>25.9239</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>26.11955</v>
+        <v>25.97296</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="D214">
-        <v>26.168479999999999</v>
+        <v>26.021930000000001</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>26.21734</v>
+        <v>26.070810000000002</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>26.26613</v>
+        <v>26.11956</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>26.31485</v>
+        <v>26.16818</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>26.36347</v>
+        <v>26.21668</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>26.411950000000001</v>
+        <v>26.265049999999999</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>26.460270000000001</v>
+        <v>26.313279999999999</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
@@ -4097,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="D221">
-        <v>26.47195</v>
+        <v>26.325089999999999</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>26.419060000000002</v>
+        <v>26.272729999999999</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.4">
@@ -4125,7 +4125,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>26.31636</v>
+        <v>26.170860000000001</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="D224">
-        <v>26.174589999999998</v>
+        <v>26.030069999999998</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.4">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="D225">
-        <v>26.001930000000002</v>
+        <v>25.858450000000001</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>25.804780000000001</v>
+        <v>25.662310000000002</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.4">
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>25.588170000000002</v>
+        <v>25.446680000000001</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>25.35613</v>
+        <v>25.215630000000001</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.4">
@@ -4209,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="D229">
-        <v>25.111879999999999</v>
+        <v>24.972390000000001</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>3</v>
       </c>
       <c r="D230">
-        <v>24.858029999999999</v>
+        <v>24.719570000000001</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.4">
@@ -4237,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>24.596720000000001</v>
+        <v>24.459309999999999</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>3</v>
       </c>
       <c r="D232">
-        <v>24.32977</v>
+        <v>24.193370000000002</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.4">
@@ -4265,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>24.05866</v>
+        <v>23.923210000000001</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D234">
-        <v>23.784610000000001</v>
+        <v>23.650020000000001</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.4">
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="D235">
-        <v>23.508610000000001</v>
+        <v>23.37482</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>23.231470000000002</v>
+        <v>23.09843</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.4">
@@ -4321,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="D237">
-        <v>22.953859999999999</v>
+        <v>22.821539999999999</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>22.71237</v>
+        <v>22.58051</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>22.535060000000001</v>
+        <v>22.403289999999998</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>22.407869999999999</v>
+        <v>22.275929999999999</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="D241">
-        <v>22.32056</v>
+        <v>22.188300000000002</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.4">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="D242">
-        <v>22.265370000000001</v>
+        <v>22.132709999999999</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.4">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>22.236229999999999</v>
+        <v>22.10313</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D244">
-        <v>22.22831</v>
+        <v>22.094750000000001</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.4">
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="D245">
-        <v>22.23771</v>
+        <v>22.103670000000001</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.4">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D246">
-        <v>22.26127</v>
+        <v>22.126760000000001</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.4">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>22.296410000000002</v>
+        <v>22.16141</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>22.341000000000001</v>
+        <v>22.205490000000001</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>22.39329</v>
+        <v>22.257259999999999</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>22.451830000000001</v>
+        <v>22.315259999999999</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.4">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>22.515360000000001</v>
+        <v>22.378260000000001</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>22.582850000000001</v>
+        <v>22.4452</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.4">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>22.653390000000002</v>
+        <v>22.5152</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.4">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>22.72626</v>
+        <v>22.58756</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.4">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>22.800889999999999</v>
+        <v>22.6617</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>22.876799999999999</v>
+        <v>22.73714</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.4">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>22.95356</v>
+        <v>22.813469999999999</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.4">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>23.030799999999999</v>
+        <v>22.890329999999999</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>23.108229999999999</v>
+        <v>22.967410000000001</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>23.185549999999999</v>
+        <v>23.044429999999998</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.4">
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>23.26249</v>
+        <v>23.121120000000001</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.4">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="D262">
-        <v>23.33887</v>
+        <v>23.19727</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="D263">
-        <v>23.41451</v>
+        <v>23.27271</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D264">
-        <v>23.48931</v>
+        <v>23.347270000000002</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.4">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>23.563130000000001</v>
+        <v>23.420860000000001</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.4">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D266">
-        <v>23.635870000000001</v>
+        <v>23.493359999999999</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="D267">
-        <v>23.707419999999999</v>
+        <v>23.564699999999998</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="D268">
-        <v>23.777719999999999</v>
+        <v>23.634810000000002</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.4">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>23.846730000000001</v>
+        <v>23.70364</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.4">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D270">
-        <v>23.91442</v>
+        <v>23.771170000000001</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>23.980779999999999</v>
+        <v>23.837389999999999</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>24.045819999999999</v>
+        <v>23.902280000000001</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="D273">
-        <v>24.109539999999999</v>
+        <v>23.965869999999999</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="D274">
-        <v>24.171970000000002</v>
+        <v>24.02816</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="D275">
-        <v>24.233139999999999</v>
+        <v>24.089179999999999</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D276">
-        <v>24.29308</v>
+        <v>24.148969999999998</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="D277">
-        <v>24.35183</v>
+        <v>24.207550000000001</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.4">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>24.40944</v>
+        <v>24.264990000000001</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.4">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>24.465959999999999</v>
+        <v>24.321339999999999</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D280">
-        <v>24.52148</v>
+        <v>24.37669</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="D281">
-        <v>24.576059999999998</v>
+        <v>24.43111</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.4">
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="D282">
-        <v>24.629750000000001</v>
+        <v>24.484670000000001</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.4">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>24.682649999999999</v>
+        <v>24.53744</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>24.734819999999999</v>
+        <v>24.589479999999998</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="D285">
-        <v>24.786349999999999</v>
+        <v>24.64086</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.4">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>24.837309999999999</v>
+        <v>24.691659999999999</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.4">
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="D287">
-        <v>24.887779999999999</v>
+        <v>24.741969999999998</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="D288">
-        <v>24.937860000000001</v>
+        <v>24.791899999999998</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.4">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="D289">
-        <v>24.9876</v>
+        <v>24.841519999999999</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.4">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>25.037099999999999</v>
+        <v>24.890920000000001</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.4">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="D291">
-        <v>25.08642</v>
+        <v>24.940149999999999</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.4">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>25.135629999999999</v>
+        <v>24.989280000000001</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.4">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D293">
-        <v>25.18478</v>
+        <v>25.03837</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.4">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="D294">
-        <v>25.233910000000002</v>
+        <v>25.08746</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.4">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="D295">
-        <v>25.283059999999999</v>
+        <v>25.136590000000002</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D296">
-        <v>25.332260000000002</v>
+        <v>25.185780000000001</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.4">
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>25.381540000000001</v>
+        <v>25.23507</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.4">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>25.43093</v>
+        <v>25.284459999999999</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.4">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>25.480419999999999</v>
+        <v>25.333960000000001</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>25.53</v>
+        <v>25.38355</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.4">
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="D301">
-        <v>25.579640000000001</v>
+        <v>25.433199999999999</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.4">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D302">
-        <v>25.62931</v>
+        <v>25.482880000000002</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.4">
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="D303">
-        <v>25.678989999999999</v>
+        <v>25.53256</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/07_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5_delta_t_60s.xlsx
+++ b/inputs/data_symbols_TD/07_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5_delta_t_60s.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5CE224F-4811-4F6A-87A8-7162DA074389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{36807299-5FD0-49FA-8A27-9BC4AD9E0139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{5CC10C9C-F663-40F5-A374-5CEAB07BFD2D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0FF34535-93D8-45A6-BA3C-42545C7ADF64}"/>
   </bookViews>
   <sheets>
     <sheet name="07_LTAN06_800km_1213COLD_MZ_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D032B1-AC77-4231-9B18-9CDCD55928E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D877B55B-2EE9-465D-A01F-1728F5220F47}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/07_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5_delta_t_60s.xlsx
+++ b/inputs/data_symbols_TD/07_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5_delta_t_60s.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36807299-5FD0-49FA-8A27-9BC4AD9E0139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD2BEB1A-7FB8-414F-92A4-431866919F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0FF34535-93D8-45A6-BA3C-42545C7ADF64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B1444C4D-480A-4BFE-BCA5-6B8BE650474C}"/>
   </bookViews>
   <sheets>
     <sheet name="07_LTAN06_800km_1213COLD_MZ_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D877B55B-2EE9-465D-A01F-1728F5220F47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA6D9DE7-D55C-4777-8644-8AB2A3B65085}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
